--- a/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
+++ b/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>①在宅生活改善調査　より適切と思われるサービス（小規模多機能44票・住宅型有料27票ほか）、区域内に事業所が存在しないサービスを選んだ票20票（20.4％）／④介護・介助が必要だが受けていない7.0％</t>
+          <t>①在宅生活改善調査　より適切と思われるサービス（小規模多機能44票・住宅型有料27票ほか）、区域内に事業所が存在しないサービスを選んだ票20票（20.2％）／④介護・介助が必要だが受けていない7.0％</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>調査とKPIの双方が対応する。H12の振替案（20.4％）はこの施策の成果を直接測る。</t>
+          <t>調査とKPIの双方が対応する。H12の振替案（20.2％）はこの施策の成果を直接測る。</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>20.4％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>H12の振替案（区域内に事業所が存在しないサービスを必要と判断された利用者20.4％）は、「必要サービス未充足率」の代理として強すぎる。ケアマネジャーが「より適切と思われる」と回答したことは、サービスが必要であることと同義ではない。</t>
+          <t>H12の振替案（区域内に事業所が存在しないサービスを必要と判断された利用者20.2％）は、「必要サービス未充足率」の代理として強すぎる。ケアマネジャーが「より適切と思われる」と回答したことは、サービスが必要であることと同義ではない。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
